--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -460,19 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.54127</v>
+        <v>16.8997</v>
       </c>
       <c r="D2" t="n">
-        <v>16.63596</v>
+        <v>16.49202</v>
       </c>
       <c r="E2" t="n">
-        <v>16.67121</v>
+        <v>16.64749</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.39936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0503</v>
+        <v>0.05108</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82869</v>
+        <v>1.81526</v>
       </c>
     </row>
     <row r="3">
@@ -482,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.61232</v>
+        <v>17.0478</v>
       </c>
       <c r="D3" t="n">
-        <v>16.93613</v>
+        <v>16.73228</v>
       </c>
       <c r="E3" t="n">
-        <v>16.93735</v>
+        <v>16.84754</v>
       </c>
       <c r="F3" t="n">
-        <v>42.1646</v>
+        <v>41.79764</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.05039</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83206</v>
+        <v>1.86162</v>
       </c>
     </row>
     <row r="4">
@@ -506,25 +509,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="C4" t="n">
+        <v>16.73102</v>
       </c>
       <c r="D4" t="n">
-        <v>16.46554</v>
+        <v>16.54475</v>
       </c>
       <c r="E4" t="n">
-        <v>16.92154</v>
+        <v>16.57707</v>
       </c>
       <c r="F4" t="n">
-        <v>42.92395</v>
+        <v>42.95487</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05151</v>
+        <v>0.05027</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83488</v>
+        <v>1.81013</v>
       </c>
     </row>
     <row r="5">
@@ -533,25 +534,23 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
+      <c r="C5" t="n">
+        <v>16.86397</v>
       </c>
       <c r="D5" t="n">
-        <v>16.60664</v>
+        <v>16.43971</v>
       </c>
       <c r="E5" t="n">
-        <v>16.61289</v>
+        <v>16.60678</v>
       </c>
       <c r="F5" t="n">
-        <v>42.5685</v>
+        <v>42.30153</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05035</v>
+        <v>0.05066</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81746</v>
+        <v>1.77373</v>
       </c>
     </row>
     <row r="6">
@@ -560,23 +559,10 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>17.24922</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16.74644</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17.25041</v>
-      </c>
-      <c r="F6" t="n">
-        <v>41.94556</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.05047</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#DIV/0!</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>scratched - not measurable</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -586,24 +572,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.96855</v>
+        <v>16.66456</v>
       </c>
       <c r="D7" t="n">
-        <v>16.40144</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 16.48 </t>
-        </is>
+        <v>16.41018</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.43479</v>
       </c>
       <c r="F7" t="n">
-        <v>42.58663</v>
+        <v>42.84341</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05033</v>
+        <v>0.0514</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81981</v>
+        <v>1.80747</v>
       </c>
     </row>
     <row r="8">
@@ -613,22 +597,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.02514</v>
+        <v>16.65599</v>
       </c>
       <c r="D8" t="n">
-        <v>16.95691</v>
+        <v>16.59389</v>
       </c>
       <c r="E8" t="n">
-        <v>16.76093</v>
+        <v>16.62205</v>
       </c>
       <c r="F8" t="n">
-        <v>43.12955</v>
+        <v>41.80926</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05052</v>
+        <v>0.05113</v>
       </c>
       <c r="H8" t="n">
-        <v>1.78575</v>
+        <v>1.79903</v>
       </c>
     </row>
     <row r="9">
@@ -638,22 +622,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.76636</v>
+        <v>16.80925</v>
       </c>
       <c r="D9" t="n">
-        <v>16.26755</v>
+        <v>16.5321</v>
       </c>
       <c r="E9" t="n">
-        <v>16.97406</v>
+        <v>16.77054</v>
       </c>
       <c r="F9" t="n">
-        <v>42.28334</v>
+        <v>43.20231</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05076</v>
+        <v>0.0516</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82505</v>
+        <v>1.84037</v>
       </c>
     </row>
     <row r="10">
@@ -663,33 +647,48 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.54066</v>
+        <v>16.84578</v>
       </c>
       <c r="D10" t="n">
-        <v>16.50964</v>
+        <v>16.38629</v>
       </c>
       <c r="E10" t="n">
-        <v>16.85012</v>
+        <v>16.58276</v>
       </c>
       <c r="F10" t="n">
-        <v>42.55704</v>
+        <v>42.86811</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05015</v>
+        <v>0.05005</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83075</v>
+        <v>1.82505</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -701,14 +700,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>16.39623</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11765</v>
+        <v>16.24841</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.39584</v>
+      </c>
+      <c r="F12" t="n">
+        <v>21.93613</v>
+      </c>
+      <c r="G12" t="n">
+        <v>34.38455</v>
       </c>
     </row>
     <row r="13">
@@ -718,10 +726,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>16.6975</v>
       </c>
       <c r="D13" t="n">
-        <v>1.09978</v>
+        <v>15.82074</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.63113</v>
+      </c>
+      <c r="F13" t="n">
+        <v>21.73231</v>
+      </c>
+      <c r="G13" t="n">
+        <v>33.82406</v>
       </c>
     </row>
     <row r="14">
@@ -730,11 +747,25 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>re-measured</t>
+        </is>
+      </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>16.74924</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11377</v>
+        <v>16.01388</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.52412</v>
+      </c>
+      <c r="F14" t="n">
+        <v>21.89043</v>
+      </c>
+      <c r="G14" t="n">
+        <v>33.97894</v>
       </c>
     </row>
     <row r="15">
@@ -744,10 +775,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>16.88866</v>
       </c>
       <c r="D15" t="n">
-        <v>1.12099</v>
+        <v>16.02105</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.48601</v>
+      </c>
+      <c r="F15" t="n">
+        <v>21.84396</v>
+      </c>
+      <c r="G15" t="n">
+        <v>34.09326</v>
       </c>
     </row>
     <row r="16">
@@ -757,10 +797,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>17.29099</v>
       </c>
       <c r="D16" t="n">
-        <v>1.10617</v>
+        <v>15.89535</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.19535</v>
+      </c>
+      <c r="F16" t="n">
+        <v>21.54262</v>
+      </c>
+      <c r="G16" t="n">
+        <v>33.84581</v>
       </c>
     </row>
     <row r="17">
@@ -770,10 +819,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>16.8118</v>
       </c>
       <c r="D17" t="n">
-        <v>1.09644</v>
+        <v>15.78051</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.48619</v>
+      </c>
+      <c r="F17" t="n">
+        <v>21.48918</v>
+      </c>
+      <c r="G17" t="n">
+        <v>34.1124</v>
       </c>
     </row>
     <row r="18">
@@ -783,10 +841,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>16.63031</v>
       </c>
       <c r="D18" t="n">
-        <v>1.12827</v>
+        <v>16.06115</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.15525</v>
+      </c>
+      <c r="F18" t="n">
+        <v>21.85303</v>
+      </c>
+      <c r="G18" t="n">
+        <v>34.15984</v>
       </c>
     </row>
     <row r="19">
@@ -796,10 +863,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>16.94074</v>
       </c>
       <c r="D19" t="n">
-        <v>1.10636</v>
+        <v>15.97933</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.23109</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21.78838</v>
+      </c>
+      <c r="G19" t="n">
+        <v>33.83325</v>
       </c>
     </row>
     <row r="20">
@@ -809,10 +885,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>16.55042</v>
       </c>
       <c r="D20" t="n">
-        <v>1.14261</v>
+        <v>16.24716</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.43836</v>
+      </c>
+      <c r="F20" t="n">
+        <v>21.52216</v>
+      </c>
+      <c r="G20" t="n">
+        <v>34.66689</v>
       </c>
     </row>
   </sheetData>
